--- a/outputs/evaluation/decision/v2/CF_M08/run_3/CF_M08_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M08/run_3/CF_M08_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,37 +506,37 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6187</v>
+        <v>0.6722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects... When the state of the subject changes, it notifies automatically all its observers, allowing that these react appropriately.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_05, Maintainability</t>
+          <t>C_05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,126 +546,76 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14a. Maintenance Requirements; Maintainability</t>
+          <t>14a. Maintenance Requirements</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Component-Based</t>
+          <t>Observer Pattern</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.7336</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects... When the subject's state changes, it automatically notifies all its observers, allowing them to react appropriately.</t>
+          <t>Docker is a containerization platform used to manage the execution of the application services.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_06, Adaptability</t>
+          <t>C_05, Maintainability</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14c. Adaptability Requirements; Adaptability</t>
+          <t>14a. Maintenance Requirements; Maintainability</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Observer Pattern</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.5961</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is used generally to manage shared resources, such as configurations, logs or database connections, where having multiple instances could lead to inconsistent states or inefficient use of resources.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C_05, Maintainability</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>14a. Maintenance Requirements; Maintainability</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Singleton Pattern</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CF_M08_AD10</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>It is designed to simplify access and database management</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.6387</v>
+        <v>0.6791</v>
       </c>
     </row>
   </sheetData>
